--- a/database/users.xlsx
+++ b/database/users.xlsx
@@ -1,44 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Users" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Users" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
-      <charset val="1"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <family val="0"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <family val="0"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <family val="0"/>
-      <sz val="10"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -58,33 +43,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="6">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
-    <cellStyle name="Currency" xfId="3" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
-    <cellStyle name="Percent" xfId="5" builtinId="5"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -157,41 +125,41 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -199,382 +167,323 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme>
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="35000">
               <a:schemeClr val="phClr">
                 <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="80000">
               <a:schemeClr val="phClr">
                 <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="40000">
               <a:schemeClr val="phClr">
                 <a:tint val="45000"/>
                 <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="80000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="30000"/>
+                <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <dimension ref="A1:M1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="1">
-      <c r="A1" s="2" t="inlineStr">
+    <row r="1">
+      <c r="A1" t="inlineStr">
         <is>
           <t>user_id</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>first_name</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>last_name</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>username</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>mobile</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>password_hash</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>supabase_user_id</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
         <is>
           <t>role</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>stp_id</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>tanker_operator_id</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>account_status</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>USR-1D13054C22</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Mohith</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Mohan</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>demandop</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>9876543210</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>mohith.mohan10102004@gmail.com</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>scrypt:32768:8:1$Z0nmBUpQGmHEvstj$ca0d7343c459fe90f7dc08e6608ef8e9c15c008b225515e8eef6dfe7244358b48d6ec0759d5dc0f377c4fdbca27c0e25ddc170c3d2d00af5f41b4e5c97cd56e6</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>demand</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-06 18:21:44</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>USR-E047F149F6</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Rajesh</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Arvind</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>stpop</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>9138918398</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>raju@something.com</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>scrypt:32768:8:1$eoLwgqN5PNxy8HAh$fb9a622ab0c4cddc513447d9368b2e14a27da4a2785db723e807de4dbc2245e99a6fc794c2f2df1f813d16560b9ddb3c00b9b8592e6807b23a9b3ba12b247b99</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>stp</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>PSTP002</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-07 10:02:16</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>USR-7309D7FE6A</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Ramesh</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Arvind</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>purvaatmos</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>9988776655</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>purvaatmosphere@gmail.com</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>scrypt:32768:8:1$UDLz0M58CkotHqa9$50d1360a21aa78f3b0748d0e232e80d18fc3a527989e6f63a47c00fe93eca301e545014ab952fa3bfadb6ea350df0f755328a769c5e9a0ecef5a578a5cba0f59</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>stp</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>PSTP009</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2026-09-07 10:20:20</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>active</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>